--- a/docs/toss_confirmation_tracking.xlsx
+++ b/docs/toss_confirmation_tracking.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="105">
   <si>
     <t xml:space="preserve">Toss Confirmation Tracking</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Key finding</t>
   </si>
   <si>
-    <t xml:space="preserve">Of 118 matches in the database, only 4 have ever had a toss actually captured — and all 4 are the most recent CPL 2026 matches (Aug 19-21, 2026). Every earlier match — 85 completed matches spanning Major League Cricket, IPL 2026, CPL 2026 (Matches 1-9), and the T20 Women's World Cup — shows no toss capture at all, i.e. check-toss never ran successfully against them.</t>
+    <t xml:space="preserve">Of 118 matches in the database, only 5 have ever had a toss actually captured — and all 5 are the most recent CPL 2026 matches (Aug 19-22, 2026). Every earlier match — 85 completed matches spanning Major League Cricket, IPL 2026, CPL 2026 (Matches 1-9), and the T20 Women's World Cup — shows no toss capture at all, i.e. check-toss never ran successfully against them.</t>
   </si>
   <si>
     <t xml:space="preserve">This matches a note already left in migrations/migration_v56_check_toss_cron.sql (dated 2026-08-18): the pg_cron job's Authorization key had gone stale from the moment the job was first written, silently 401'ing every single run — so check-toss never actually executed until that key was fixed, right around 2026-08-18/19. The data lines up exactly: nothing was ever captured before that, and the first matches to fall inside the check-toss window afterward all show activity.</t>
@@ -76,6 +76,12 @@
     <t xml:space="preserve">Started 2026-08-21 23:00 UTC — confirmed 6 min BEFORE start (cricketaddictor). On target — 3rd confirmation in a row since the fix.</t>
   </si>
   <si>
+    <t xml:space="preserve">Match 14 (CPL 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Started 2026-08-22 23:00 UTC — confirmed 10 min BEFORE start (cricketaddictor). First match checked under the widened 30-min window (deployed 2026-08-22); toss still landed ~10 min out, same as before — the wider window gives more polling passes, not an earlier source report.</t>
+  </si>
+  <si>
     <t xml:space="preserve">At a glance (live — recalculates as new daily pulls are appended to Match Detail)</t>
   </si>
   <si>
@@ -103,7 +109,7 @@
     <t xml:space="preserve">Re-run the same Supabase query against the matches table (id, tournament, match_number, teams, start_time, toss_status, toss_winner_name, toss_decision, toss_source, toss_checked_at) and append any new/updated rows to the Match Detail tab, keeping the same columns and formulas (drag column H:Q down for new rows). The Daily Summary tab will pick up new dates automatically once a row for that date exists on Match Detail with a matching Match Date (ET) value in column I. Ask me to pull a fresh export any day and I'll keep this workbook current.</t>
   </si>
   <si>
-    <t xml:space="preserve">Data pulled: 2026-08-22 (America/New_York). Source: Supabase project gepltclaeczgtruvekci, table "matches".</t>
+    <t xml:space="preserve">Data pulled: 2026-08-23 (America/New_York). Source: Supabase project gepltclaeczgtruvekci, table "matches".</t>
   </si>
   <si>
     <t xml:space="preserve">Tournament</t>
@@ -824,7 +830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:H43"/>
+  <dimension ref="B2:H44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1032,89 +1038,93 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3" t="s">
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="C28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7" t="n">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7" t="n">
         <f aca="false">COUNTA('Match Detail'!$J$2:$J$119)</f>
         <v>118</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7" t="n">
-        <f aca="false">COUNTIF('Match Detail'!$Q$2:$Q$119,"Yes")</f>
-        <v>4</v>
-      </c>
-    </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="7" t="n">
-        <f aca="false">COUNTIF('Match Detail'!$J$2:$J$119,"confirmed")</f>
-        <v>3</v>
+        <f aca="false">COUNTIF('Match Detail'!$Q$2:$Q$119,"Yes")</f>
+        <v>5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="7" t="n">
-        <f aca="false">COUNTIF('Match Detail'!$J$2:$J$119,"delay_flagged")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF('Match Detail'!$J$2:$J$119,"confirmed")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="7" t="n">
-        <f aca="false">COUNTIF('Match Detail'!$Q$2:$Q$119,"No")</f>
-        <v>114</v>
+        <f aca="false">COUNTIF('Match Detail'!$J$2:$J$119,"delay_flagged")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="7" t="n">
+        <f aca="false">COUNTIF('Match Detail'!$Q$2:$Q$119,"No")</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="8" t="n">
         <f aca="false">IFERROR(AVERAGEIFS('Match Detail'!$P$2:$P$119,'Match Detail'!$J$2:$J$119,"confirmed"),"n/a")</f>
-        <v>-8.96666666666667</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4"/>
+        <v>-9.225</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -1140,13 +1150,22 @@
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="2" t="s">
-        <v>25</v>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B6:H10"/>
     <mergeCell ref="B13:H16"/>
     <mergeCell ref="B18:H21"/>
@@ -1154,13 +1173,14 @@
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C27:H27"/>
-    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="C28:H28"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B38:H41"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B39:H42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1199,73 +1219,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="10" t="n">
         <v>63</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>46160.5833333333</v>
@@ -1279,7 +1299,7 @@
         <v>46160</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -1300,20 +1320,20 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="10" t="n">
         <v>64</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>46</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>46161.5833333333</v>
@@ -1327,7 +1347,7 @@
         <v>46161</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
@@ -1348,20 +1368,20 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>65</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>46162.5833333333</v>
@@ -1375,7 +1395,7 @@
         <v>46162</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
@@ -1396,20 +1416,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>66</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>46163.5833333333</v>
@@ -1423,7 +1443,7 @@
         <v>46163</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
@@ -1444,20 +1464,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>67</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>46164.5833333333</v>
@@ -1471,7 +1491,7 @@
         <v>46164</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
@@ -1492,20 +1512,20 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>68</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>46</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>46165.5833333333</v>
@@ -1519,7 +1539,7 @@
         <v>46165</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -1540,20 +1560,20 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>69</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="F8" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>46166.4166666667</v>
@@ -1567,7 +1587,7 @@
         <v>46166</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
@@ -1588,20 +1608,20 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" s="10" t="n">
         <v>70</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>46166.5833333333</v>
@@ -1615,7 +1635,7 @@
         <v>46166</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
@@ -1636,20 +1656,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B10" s="10" t="n">
         <v>71</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>46168.5833333333</v>
@@ -1663,7 +1683,7 @@
         <v>46168</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
@@ -1684,20 +1704,20 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" s="10" t="n">
         <v>72</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>46169.5833333333</v>
@@ -1711,7 +1731,7 @@
         <v>46169</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
@@ -1732,20 +1752,20 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" s="10" t="n">
         <v>73</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>46171.5833333333</v>
@@ -1759,7 +1779,7 @@
         <v>46171</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -1780,20 +1800,20 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>74</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>46173.5833333333</v>
@@ -1807,7 +1827,7 @@
         <v>46173</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
@@ -1828,20 +1848,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>46185.7291666667</v>
@@ -1855,7 +1875,7 @@
         <v>46185</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
@@ -1876,20 +1896,20 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>46186.3958333333</v>
@@ -1903,7 +1923,7 @@
         <v>46186</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
@@ -1924,20 +1944,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>46186.5625</v>
@@ -1951,7 +1971,7 @@
         <v>46186</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
@@ -1972,20 +1992,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" s="10" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>46186.7291666667</v>
@@ -1999,7 +2019,7 @@
         <v>46186</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
@@ -2020,20 +2040,20 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B18" s="10" t="n">
         <v>5</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>46187.3958333333</v>
@@ -2047,7 +2067,7 @@
         <v>46187</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
@@ -2068,20 +2088,20 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>6</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" s="11" t="n">
         <v>46187.5625</v>
@@ -2095,7 +2115,7 @@
         <v>46187</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
@@ -2116,20 +2136,20 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B20" s="10" t="n">
         <v>7</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>46189.5625</v>
@@ -2143,7 +2163,7 @@
         <v>46189</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
@@ -2164,20 +2184,20 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B21" s="10" t="n">
         <v>8</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>46189.7291666667</v>
@@ -2191,7 +2211,7 @@
         <v>46189</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
@@ -2212,20 +2232,20 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>9</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>46190.3958333333</v>
@@ -2239,7 +2259,7 @@
         <v>46190</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
@@ -2260,20 +2280,20 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="10" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>46190.5625</v>
@@ -2287,7 +2307,7 @@
         <v>46190</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
@@ -2308,20 +2328,20 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="10" t="n">
         <v>11</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>46190.7291666667</v>
@@ -2335,7 +2355,7 @@
         <v>46190</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
@@ -2356,20 +2376,20 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="10" t="n">
         <v>12</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>46191.7291666667</v>
@@ -2383,7 +2403,7 @@
         <v>46191</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
@@ -2404,20 +2424,20 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>46192.0208333333</v>
@@ -2431,7 +2451,7 @@
         <v>46191</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
@@ -2452,20 +2472,20 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B27" s="10" t="n">
         <v>13</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>46192.7291666667</v>
@@ -2479,7 +2499,7 @@
         <v>46192</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
@@ -2500,20 +2520,20 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B28" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>46192.8541666667</v>
@@ -2527,7 +2547,7 @@
         <v>46192</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
@@ -2548,20 +2568,20 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B29" s="10" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>46193.0520833333</v>
@@ -2575,7 +2595,7 @@
         <v>46192</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
@@ -2596,20 +2616,20 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B30" s="10" t="n">
         <v>14</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>46193.3958333333</v>
@@ -2623,7 +2643,7 @@
         <v>46193</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
@@ -2644,20 +2664,20 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>15</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G31" s="11" t="n">
         <v>46193.5625</v>
@@ -2671,7 +2691,7 @@
         <v>46193</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
@@ -2692,20 +2712,20 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>16</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>46193.7291666667</v>
@@ -2719,7 +2739,7 @@
         <v>46193</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
@@ -2740,20 +2760,20 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>4</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>71</v>
-      </c>
       <c r="F33" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G33" s="11" t="n">
         <v>46193.8541666667</v>
@@ -2767,7 +2787,7 @@
         <v>46193</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
@@ -2788,20 +2808,20 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B34" s="10" t="n">
         <v>5</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>46194.0208333333</v>
@@ -2815,7 +2835,7 @@
         <v>46193</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
@@ -2836,20 +2856,20 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B35" s="10" t="n">
         <v>17</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G35" s="11" t="n">
         <v>46194.3958333333</v>
@@ -2863,7 +2883,7 @@
         <v>46194</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
@@ -2884,20 +2904,20 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B36" s="10" t="n">
         <v>18</v>
       </c>
       <c r="C36" s="10"/>
       <c r="D36" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>46194.5625</v>
@@ -2911,7 +2931,7 @@
         <v>46194</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
@@ -2932,20 +2952,20 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B37" s="10" t="n">
         <v>6</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E37" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="F37" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>46194.8541666667</v>
@@ -2959,7 +2979,7 @@
         <v>46194</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
@@ -2980,20 +3000,20 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B38" s="10" t="n">
         <v>7</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>46195.0208333333</v>
@@ -3007,7 +3027,7 @@
         <v>46194</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
@@ -3028,20 +3048,20 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B39" s="10" t="n">
         <v>19</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>46196.3958333333</v>
@@ -3055,7 +3075,7 @@
         <v>46196</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
@@ -3076,20 +3096,20 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" s="10" t="n">
         <v>20</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>46196.5625</v>
@@ -3103,7 +3123,7 @@
         <v>46196</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
@@ -3124,20 +3144,20 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B41" s="10" t="n">
         <v>21</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G41" s="11" t="n">
         <v>46196.7291666667</v>
@@ -3151,7 +3171,7 @@
         <v>46196</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
@@ -3172,20 +3192,20 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="10" t="n">
         <v>22</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>46197.7291666667</v>
@@ -3199,7 +3219,7 @@
         <v>46197</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
@@ -3220,20 +3240,20 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B43" s="10" t="n">
         <v>8</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>71</v>
-      </c>
       <c r="F43" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>46198.0625</v>
@@ -3247,7 +3267,7 @@
         <v>46197</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
@@ -3268,20 +3288,20 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>23</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>46198.5625</v>
@@ -3295,7 +3315,7 @@
         <v>46198</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
@@ -3316,20 +3336,20 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>24</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>46198.7291666667</v>
@@ -3343,7 +3363,7 @@
         <v>46198</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
@@ -3364,20 +3384,20 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>9</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>46199.0625</v>
@@ -3391,7 +3411,7 @@
         <v>46198</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
@@ -3412,20 +3432,20 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>25</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>58</v>
-      </c>
       <c r="F47" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>46199.7291666667</v>
@@ -3439,7 +3459,7 @@
         <v>46199</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
@@ -3460,20 +3480,20 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>10</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>46199.8958333333</v>
@@ -3487,7 +3507,7 @@
         <v>46199</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
@@ -3508,20 +3528,20 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>11</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G49" s="11" t="n">
         <v>46200.0625</v>
@@ -3535,7 +3555,7 @@
         <v>46199</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
@@ -3556,20 +3576,20 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>26</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G50" s="11" t="n">
         <v>46200.3958333333</v>
@@ -3583,7 +3603,7 @@
         <v>46200</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
@@ -3604,20 +3624,20 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>27</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>46200.5625</v>
@@ -3631,7 +3651,7 @@
         <v>46200</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
@@ -3652,20 +3672,20 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>28</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G52" s="11" t="n">
         <v>46200.7291666667</v>
@@ -3679,7 +3699,7 @@
         <v>46200</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
@@ -3700,20 +3720,20 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>12</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G53" s="11" t="n">
         <v>46200.8958333333</v>
@@ -3727,7 +3747,7 @@
         <v>46200</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
@@ -3748,20 +3768,20 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>13</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G54" s="11" t="n">
         <v>46201.0625</v>
@@ -3775,7 +3795,7 @@
         <v>46200</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
@@ -3796,20 +3816,20 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B55" s="10" t="n">
         <v>29</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G55" s="11" t="n">
         <v>46201.3958333333</v>
@@ -3823,7 +3843,7 @@
         <v>46201</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
@@ -3844,20 +3864,20 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B56" s="10" t="n">
         <v>30</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G56" s="11" t="n">
         <v>46201.5625</v>
@@ -3871,7 +3891,7 @@
         <v>46201</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
@@ -3892,20 +3912,20 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B57" s="10" t="n">
         <v>14</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="F57" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G57" s="11" t="n">
         <v>46201.8958333333</v>
@@ -3919,7 +3939,7 @@
         <v>46201</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
@@ -3940,20 +3960,20 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B58" s="10" t="n">
         <v>15</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G58" s="11" t="n">
         <v>46202.0625</v>
@@ -3967,7 +3987,7 @@
         <v>46201</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
@@ -3988,18 +4008,18 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
       <c r="D59" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G59" s="11" t="n">
         <v>46203.5625</v>
@@ -4013,7 +4033,7 @@
         <v>46203</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
@@ -4034,20 +4054,20 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B60" s="10" t="n">
         <v>16</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G60" s="11" t="n">
         <v>46205.0625</v>
@@ -4061,7 +4081,7 @@
         <v>46204</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
@@ -4082,18 +4102,18 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
       <c r="D61" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G61" s="11" t="n">
         <v>46205.7291666667</v>
@@ -4107,7 +4127,7 @@
         <v>46205</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
@@ -4128,20 +4148,20 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B62" s="10" t="n">
         <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G62" s="11" t="n">
         <v>46206.0625</v>
@@ -4155,7 +4175,7 @@
         <v>46205</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
@@ -4176,20 +4196,20 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B63" s="10" t="n">
         <v>18</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G63" s="11" t="n">
         <v>46207.0625</v>
@@ -4203,7 +4223,7 @@
         <v>46206</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
@@ -4224,20 +4244,20 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B64" s="10" t="n">
         <v>19</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G64" s="11" t="n">
         <v>46207.8958333333</v>
@@ -4251,7 +4271,7 @@
         <v>46207</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
@@ -4272,20 +4292,20 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B65" s="10" t="n">
         <v>20</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G65" s="11" t="n">
         <v>46208.0625</v>
@@ -4299,7 +4319,7 @@
         <v>46207</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
@@ -4320,18 +4340,18 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G66" s="11" t="n">
         <v>46208.5625</v>
@@ -4345,7 +4365,7 @@
         <v>46208</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
@@ -4366,20 +4386,20 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B67" s="10" t="n">
         <v>21</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G67" s="11" t="n">
         <v>46208.8958333333</v>
@@ -4393,7 +4413,7 @@
         <v>46208</v>
       </c>
       <c r="J67" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
@@ -4414,20 +4434,20 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B68" s="10" t="n">
         <v>22</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="F68" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G68" s="11" t="n">
         <v>46209.0625</v>
@@ -4441,7 +4461,7 @@
         <v>46208</v>
       </c>
       <c r="J68" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
@@ -4462,20 +4482,20 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B69" s="10" t="n">
         <v>23</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E69" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="F69" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G69" s="11" t="n">
         <v>46212.0208333333</v>
@@ -4489,7 +4509,7 @@
         <v>46211</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
@@ -4510,20 +4530,20 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B70" s="10" t="n">
         <v>24</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G70" s="11" t="n">
         <v>46213.0208333333</v>
@@ -4537,7 +4557,7 @@
         <v>46212</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
@@ -4558,20 +4578,20 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B71" s="10" t="n">
         <v>25</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G71" s="11" t="n">
         <v>46213.8541666667</v>
@@ -4585,7 +4605,7 @@
         <v>46213</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
@@ -4606,20 +4626,20 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B72" s="10" t="n">
         <v>26</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G72" s="11" t="n">
         <v>46214.0208333333</v>
@@ -4633,7 +4653,7 @@
         <v>46213</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
@@ -4654,20 +4674,20 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B73" s="10" t="n">
         <v>27</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G73" s="11" t="n">
         <v>46214.8541666667</v>
@@ -4681,7 +4701,7 @@
         <v>46214</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
@@ -4702,20 +4722,20 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B74" s="10" t="n">
         <v>28</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G74" s="11" t="n">
         <v>46215.0208333333</v>
@@ -4729,7 +4749,7 @@
         <v>46214</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
@@ -4750,20 +4770,20 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B75" s="10" t="n">
         <v>29</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G75" s="11" t="n">
         <v>46215.8541666667</v>
@@ -4777,7 +4797,7 @@
         <v>46215</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
@@ -4798,20 +4818,20 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B76" s="10" t="n">
         <v>30</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G76" s="11" t="n">
         <v>46216.0208333333</v>
@@ -4825,7 +4845,7 @@
         <v>46215</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
@@ -4846,22 +4866,22 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B77" s="10" t="n">
         <v>31</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G77" s="11" t="n">
         <v>46218.8958333333</v>
@@ -4875,7 +4895,7 @@
         <v>46218</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
@@ -4896,22 +4916,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B78" s="10" t="n">
         <v>32</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G78" s="11" t="n">
         <v>46219.0729166667</v>
@@ -4925,7 +4945,7 @@
         <v>46218</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
@@ -4946,22 +4966,22 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B79" s="10" t="n">
         <v>33</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G79" s="11" t="n">
         <v>46220.0625</v>
@@ -4975,7 +4995,7 @@
         <v>46219</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
@@ -4996,22 +5016,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B80" s="10" t="n">
         <v>34</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G80" s="11" t="n">
         <v>46221.9791666667</v>
@@ -5025,7 +5045,7 @@
         <v>46221</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
@@ -5046,20 +5066,20 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B81" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G81" s="11" t="n">
         <v>46241.9583333333</v>
@@ -5073,7 +5093,7 @@
         <v>46241</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
@@ -5094,20 +5114,20 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B82" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G82" s="11" t="n">
         <v>46242.9583333333</v>
@@ -5121,7 +5141,7 @@
         <v>46242</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
@@ -5142,20 +5162,20 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" s="10" t="n">
         <v>3</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G83" s="11" t="n">
         <v>46243.9583333333</v>
@@ -5169,7 +5189,7 @@
         <v>46243</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
@@ -5190,20 +5210,20 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B84" s="10" t="n">
         <v>4</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G84" s="11" t="n">
         <v>46245.9166666667</v>
@@ -5217,7 +5237,7 @@
         <v>46245</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
@@ -5238,20 +5258,20 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="10" t="n">
         <v>5</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E85" s="10" t="s">
-        <v>85</v>
-      </c>
       <c r="F85" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G85" s="11" t="n">
         <v>46246.9583333333</v>
@@ -5265,7 +5285,7 @@
         <v>46246</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K85" s="10"/>
       <c r="L85" s="10"/>
@@ -5286,20 +5306,20 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B86" s="10" t="n">
         <v>6</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G86" s="11" t="n">
         <v>46248</v>
@@ -5313,7 +5333,7 @@
         <v>46247</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K86" s="10"/>
       <c r="L86" s="10"/>
@@ -5334,20 +5354,20 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B87" s="10" t="n">
         <v>7</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G87" s="11" t="n">
         <v>46248.9583333333</v>
@@ -5361,7 +5381,7 @@
         <v>46248</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K87" s="10"/>
       <c r="L87" s="10"/>
@@ -5382,20 +5402,20 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B88" s="10" t="n">
         <v>8</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G88" s="11" t="n">
         <v>46250</v>
@@ -5409,7 +5429,7 @@
         <v>46249</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K88" s="10"/>
       <c r="L88" s="10"/>
@@ -5430,20 +5450,20 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B89" s="10" t="n">
         <v>9</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G89" s="11" t="n">
         <v>46250.9583333333</v>
@@ -5457,7 +5477,7 @@
         <v>46250</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K89" s="10"/>
       <c r="L89" s="10"/>
@@ -5478,20 +5498,20 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B90" s="10" t="n">
         <v>10</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G90" s="11" t="n">
         <v>46253</v>
@@ -5505,7 +5525,7 @@
         <v>46252</v>
       </c>
       <c r="J90" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K90" s="10"/>
       <c r="L90" s="10"/>
@@ -5528,20 +5548,20 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B91" s="10" t="n">
         <v>11</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E91" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="E91" s="10" t="s">
-        <v>87</v>
-      </c>
       <c r="F91" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G91" s="11" t="n">
         <v>46253.9583333333</v>
@@ -5555,16 +5575,16 @@
         <v>46253</v>
       </c>
       <c r="J91" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K91" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K91" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="L91" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N91" s="11" t="n">
         <v>46253.9486147454</v>
@@ -5584,20 +5604,20 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B92" s="10" t="n">
         <v>12</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G92" s="11" t="n">
         <v>46254.9583333333</v>
@@ -5611,16 +5631,16 @@
         <v>46254</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L92" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N92" s="11" t="n">
         <v>46254.9534757176</v>
@@ -5640,20 +5660,20 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B93" s="10" t="n">
         <v>13</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G93" s="11" t="n">
         <v>46255.9583333333</v>
@@ -5667,16 +5687,16 @@
         <v>46255</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K93" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L93" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N93" s="11" t="n">
         <v>46255.9542029745</v>
@@ -5696,20 +5716,20 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B94" s="10" t="n">
         <v>14</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>46256.9583333333</v>
@@ -5723,55 +5743,63 @@
         <v>46256</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="11" t="str">
+        <v>93</v>
+      </c>
+      <c r="K94" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L94" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="N94" s="11" t="n">
+        <v>46256.9513967361</v>
+      </c>
+      <c r="O94" s="11" t="n">
         <f aca="false">IF(N94="","",N94-TIME(4,0,0))</f>
-        <v/>
-      </c>
-      <c r="P94" s="13" t="str">
+        <v>46256.7847300695</v>
+      </c>
+      <c r="P94" s="13" t="n">
         <f aca="false">IF(N94="","",ROUND((N94-G94)*1440,1))</f>
-        <v/>
+        <v>-10</v>
       </c>
       <c r="Q94" s="10" t="str">
         <f aca="false">IF(N94="","No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B95" s="10" t="n">
         <v>15</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G95" s="11" t="n">
-        <v>46257.9583333333</v>
+        <v>46257.96875</v>
       </c>
       <c r="H95" s="11" t="n">
         <f aca="false">G95-TIME(4,0,0)</f>
-        <v>46257.7916666667</v>
+        <v>46257.8020833333</v>
       </c>
       <c r="I95" s="12" t="n">
         <f aca="false">INT(H95)</f>
         <v>46257</v>
       </c>
       <c r="J95" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K95" s="10"/>
       <c r="L95" s="10"/>
@@ -5792,20 +5820,20 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B96" s="10" t="n">
         <v>16</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G96" s="11" t="n">
         <v>46259.9583333333</v>
@@ -5819,7 +5847,7 @@
         <v>46259</v>
       </c>
       <c r="J96" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K96" s="10"/>
       <c r="L96" s="10"/>
@@ -5840,20 +5868,20 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B97" s="10" t="n">
         <v>17</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G97" s="11" t="n">
         <v>46260.9583333333</v>
@@ -5867,7 +5895,7 @@
         <v>46260</v>
       </c>
       <c r="J97" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K97" s="10"/>
       <c r="L97" s="10"/>
@@ -5888,20 +5916,20 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B98" s="10" t="n">
         <v>18</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G98" s="11" t="n">
         <v>46261.9583333333</v>
@@ -5915,7 +5943,7 @@
         <v>46261</v>
       </c>
       <c r="J98" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K98" s="10"/>
       <c r="L98" s="10"/>
@@ -5936,20 +5964,20 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B99" s="10" t="n">
         <v>19</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E99" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E99" s="10" t="s">
-        <v>86</v>
-      </c>
       <c r="F99" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G99" s="11" t="n">
         <v>46263</v>
@@ -5963,7 +5991,7 @@
         <v>46262</v>
       </c>
       <c r="J99" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K99" s="10"/>
       <c r="L99" s="10"/>
@@ -5984,20 +6012,20 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B100" s="10" t="n">
         <v>20</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G100" s="11" t="n">
         <v>46263.9583333333</v>
@@ -6011,7 +6039,7 @@
         <v>46263</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K100" s="10"/>
       <c r="L100" s="10"/>
@@ -6032,20 +6060,20 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B101" s="10" t="n">
         <v>21</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>46264.9583333333</v>
@@ -6059,7 +6087,7 @@
         <v>46264</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K101" s="10"/>
       <c r="L101" s="10"/>
@@ -6080,20 +6108,20 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B102" s="10" t="n">
         <v>22</v>
       </c>
       <c r="C102" s="10"/>
       <c r="D102" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G102" s="11" t="n">
         <v>46265.875</v>
@@ -6107,7 +6135,7 @@
         <v>46265</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K102" s="10"/>
       <c r="L102" s="10"/>
@@ -6128,20 +6156,20 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B103" s="10" t="n">
         <v>23</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G103" s="11" t="n">
         <v>46266.9583333333</v>
@@ -6155,7 +6183,7 @@
         <v>46266</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
@@ -6176,20 +6204,20 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B104" s="10" t="n">
         <v>24</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G104" s="11" t="n">
         <v>46267.9583333333</v>
@@ -6203,7 +6231,7 @@
         <v>46267</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K104" s="10"/>
       <c r="L104" s="10"/>
@@ -6224,20 +6252,20 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B105" s="10" t="n">
         <v>25</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E105" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E105" s="10" t="s">
-        <v>85</v>
-      </c>
       <c r="F105" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>46268.9583333333</v>
@@ -6251,7 +6279,7 @@
         <v>46268</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K105" s="10"/>
       <c r="L105" s="10"/>
@@ -6272,20 +6300,20 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B106" s="10" t="n">
         <v>26</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G106" s="11" t="n">
         <v>46269.9583333333</v>
@@ -6299,7 +6327,7 @@
         <v>46269</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K106" s="10"/>
       <c r="L106" s="10"/>
@@ -6320,20 +6348,20 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B107" s="10" t="n">
         <v>27</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E107" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E107" s="10" t="s">
-        <v>86</v>
-      </c>
       <c r="F107" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G107" s="11" t="n">
         <v>46271</v>
@@ -6347,7 +6375,7 @@
         <v>46270</v>
       </c>
       <c r="J107" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K107" s="10"/>
       <c r="L107" s="10"/>
@@ -6368,20 +6396,20 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B108" s="10" t="n">
         <v>28</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G108" s="11" t="n">
         <v>46271.5833333333</v>
@@ -6395,7 +6423,7 @@
         <v>46271</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K108" s="10"/>
       <c r="L108" s="10"/>
@@ -6416,20 +6444,20 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B109" s="10" t="n">
         <v>29</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G109" s="11" t="n">
         <v>46271.9583333333</v>
@@ -6443,7 +6471,7 @@
         <v>46271</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K109" s="10"/>
       <c r="L109" s="10"/>
@@ -6464,20 +6492,20 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B110" s="10" t="n">
         <v>30</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>46273.9583333333</v>
@@ -6491,7 +6519,7 @@
         <v>46273</v>
       </c>
       <c r="J110" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K110" s="10"/>
       <c r="L110" s="10"/>
@@ -6512,20 +6540,20 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B111" s="10" t="n">
         <v>31</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E111" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="E111" s="10" t="s">
-        <v>87</v>
-      </c>
       <c r="F111" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G111" s="11" t="n">
         <v>46274.9583333333</v>
@@ -6539,7 +6567,7 @@
         <v>46274</v>
       </c>
       <c r="J111" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K111" s="10"/>
       <c r="L111" s="10"/>
@@ -6560,20 +6588,20 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B112" s="10" t="n">
         <v>32</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G112" s="11" t="n">
         <v>46275.9583333333</v>
@@ -6587,7 +6615,7 @@
         <v>46275</v>
       </c>
       <c r="J112" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K112" s="10"/>
       <c r="L112" s="10"/>
@@ -6608,20 +6636,20 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B113" s="10" t="n">
         <v>33</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G113" s="11" t="n">
         <v>46276.9583333333</v>
@@ -6635,7 +6663,7 @@
         <v>46276</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K113" s="10"/>
       <c r="L113" s="10"/>
@@ -6656,20 +6684,20 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B114" s="10" t="n">
         <v>34</v>
       </c>
       <c r="C114" s="10"/>
       <c r="D114" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G114" s="11" t="n">
         <v>46278</v>
@@ -6683,7 +6711,7 @@
         <v>46277</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K114" s="10"/>
       <c r="L114" s="10"/>
@@ -6704,20 +6732,20 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B115" s="10" t="n">
         <v>35</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G115" s="11" t="n">
         <v>46278.9583333333</v>
@@ -6731,7 +6759,7 @@
         <v>46278</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K115" s="10"/>
       <c r="L115" s="10"/>
@@ -6752,22 +6780,22 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B116" s="10" t="n">
         <v>36</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G116" s="11" t="n">
         <v>46281.9583333333</v>
@@ -6781,7 +6809,7 @@
         <v>46281</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K116" s="10"/>
       <c r="L116" s="10"/>
@@ -6802,22 +6830,22 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B117" s="10" t="n">
         <v>37</v>
       </c>
       <c r="C117" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D117" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D117" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="E117" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G117" s="11" t="n">
         <v>46283</v>
@@ -6831,7 +6859,7 @@
         <v>46282</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K117" s="10"/>
       <c r="L117" s="10"/>
@@ -6852,22 +6880,22 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B118" s="10" t="n">
         <v>38</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G118" s="11" t="n">
         <v>46283.9583333333</v>
@@ -6881,7 +6909,7 @@
         <v>46283</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K118" s="10"/>
       <c r="L118" s="10"/>
@@ -6902,22 +6930,22 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B119" s="10" t="n">
         <v>39</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G119" s="11" t="n">
         <v>46285.9583333333</v>
@@ -6931,7 +6959,7 @@
         <v>46285</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K119" s="10"/>
       <c r="L119" s="10"/>
@@ -6981,28 +7009,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8764,11 +8792,11 @@
       </c>
       <c r="C55" s="10" t="n">
         <f aca="false">COUNTIFS('Match Detail'!$I$2:$I$119,$A55,'Match Detail'!$Q$2:$Q$119,"Yes")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="10" t="n">
         <f aca="false">COUNTIFS('Match Detail'!$I$2:$I$119,$A55,'Match Detail'!$J$2:$J$119,"confirmed")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="10" t="n">
         <f aca="false">COUNTIFS('Match Detail'!$I$2:$I$119,$A55,'Match Detail'!$J$2:$J$119,"delay_flagged")</f>
@@ -8776,15 +8804,15 @@
       </c>
       <c r="F55" s="10" t="n">
         <f aca="false">B55-C55</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="15" t="n">
         <f aca="false">IF(B55=0,0,C55/B55)</f>
-        <v>0</v>
-      </c>
-      <c r="H55" s="13" t="str">
+        <v>1</v>
+      </c>
+      <c r="H55" s="13" t="n">
         <f aca="false">IFERROR(AVERAGEIFS('Match Detail'!$P$2:$P$119,'Match Detail'!$I$2:$I$119,$A55,'Match Detail'!$J$2:$J$119,"confirmed"),"")</f>
-        <v/>
+        <v>-10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
